--- a/artfynd/A 22808-2025 artfynd.xlsx
+++ b/artfynd/A 22808-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124966090</v>
+        <v>124966096</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -796,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124966096</v>
+        <v>124966090</v>
       </c>
       <c r="B3" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 22808-2025 artfynd.xlsx
+++ b/artfynd/A 22808-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124966096</v>
+        <v>124966090</v>
       </c>
       <c r="B2" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -800,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124966090</v>
+        <v>124966096</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,30 +808,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 22808-2025 artfynd.xlsx
+++ b/artfynd/A 22808-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124966096</v>
+        <v>124966090</v>
       </c>
       <c r="B2" t="n">
-        <v>79926</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -800,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124966090</v>
+        <v>124966096</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>80063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,30 +808,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 22808-2025 artfynd.xlsx
+++ b/artfynd/A 22808-2025 artfynd.xlsx
@@ -675,42 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124966090</v>
+        <v>124966096</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -796,46 +795,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124966096</v>
+        <v>124966090</v>
       </c>
       <c r="B3" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 22808-2025 artfynd.xlsx
+++ b/artfynd/A 22808-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124966096</v>
+        <v>124966090</v>
       </c>
       <c r="B2" t="n">
-        <v>80063</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,37 +791,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124966090</v>
+        <v>124966096</v>
       </c>
       <c r="B3" t="n">
-        <v>80028</v>
+        <v>80467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -908,6 +908,228 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121463489</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Edsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>580848</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7025966</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lindy Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lindy Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121463488</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Edsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580848</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7025966</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lindy Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lindy Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22808-2025 artfynd.xlsx
+++ b/artfynd/A 22808-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124966090</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124966096</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121463489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,8 +1150,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121463488</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>